--- a/B2_seg推論統計_11n.xlsx
+++ b/B2_seg推論統計_11n.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,15 +449,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>最大mask剔除碎塊數</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Mask_mAP50-95</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>GT數</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>狀態</t>
         </is>
@@ -484,15 +489,18 @@
         <v>0.9482</v>
       </c>
       <c r="F2" t="n">
-        <v>460</v>
+        <v>1345</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>0.995</v>
       </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -519,15 +527,18 @@
         <v>0.9609</v>
       </c>
       <c r="F3" t="n">
-        <v>487</v>
+        <v>1344</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -548,21 +559,24 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>79944</v>
+        <v>79942</v>
       </c>
       <c r="E4" t="n">
         <v>0.9492</v>
       </c>
       <c r="F4" t="n">
-        <v>506</v>
+        <v>1372</v>
       </c>
       <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
         <v>0.995</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -583,21 +597,24 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>62047.5</v>
+        <v>62037.5</v>
       </c>
       <c r="E5" t="n">
         <v>0.9471000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>498</v>
+        <v>1309</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8955</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -618,21 +635,24 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>82884.5</v>
+        <v>82880</v>
       </c>
       <c r="E6" t="n">
         <v>0.9505</v>
       </c>
       <c r="F6" t="n">
-        <v>550</v>
+        <v>1362</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -653,21 +673,24 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>83198</v>
+        <v>83196</v>
       </c>
       <c r="E7" t="n">
         <v>0.9592000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>492</v>
+        <v>1310</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>0.995</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -694,15 +717,18 @@
         <v>0.9492</v>
       </c>
       <c r="F8" t="n">
-        <v>418</v>
+        <v>1348</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -723,21 +749,24 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>72011.5</v>
+        <v>72005.5</v>
       </c>
       <c r="E9" t="n">
         <v>0.9473</v>
       </c>
       <c r="F9" t="n">
-        <v>444</v>
+        <v>1317</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -764,15 +793,18 @@
         <v>0.9612000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>501</v>
+        <v>1348</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -799,15 +831,18 @@
         <v>0.9584</v>
       </c>
       <c r="F11" t="n">
-        <v>494</v>
+        <v>1300</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -834,15 +869,18 @@
         <v>0.9560999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>487</v>
+        <v>1294</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -863,21 +901,24 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>73817.5</v>
+        <v>72664</v>
       </c>
       <c r="E13" t="n">
         <v>0.9621</v>
       </c>
       <c r="F13" t="n">
-        <v>607</v>
+        <v>1248</v>
       </c>
       <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.796</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -904,15 +945,18 @@
         <v>0.9442</v>
       </c>
       <c r="F14" t="n">
-        <v>428</v>
+        <v>1337</v>
       </c>
       <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.995</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -939,15 +983,18 @@
         <v>0.9552</v>
       </c>
       <c r="F15" t="n">
-        <v>402</v>
+        <v>1311</v>
       </c>
       <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
         <v>0.995</v>
       </c>
-      <c r="H15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -974,15 +1021,18 @@
         <v>0.949</v>
       </c>
       <c r="F16" t="n">
-        <v>426</v>
+        <v>1244</v>
       </c>
       <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.675</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>2</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1009,15 +1059,18 @@
         <v>0.955</v>
       </c>
       <c r="F17" t="n">
-        <v>365</v>
+        <v>1319</v>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>0.995</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1044,15 +1097,18 @@
         <v>0.9475</v>
       </c>
       <c r="F18" t="n">
-        <v>461</v>
+        <v>1349</v>
       </c>
       <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.995</v>
       </c>
-      <c r="H18" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1073,21 +1129,24 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>75528.5</v>
+        <v>75484</v>
       </c>
       <c r="E19" t="n">
         <v>0.9516</v>
       </c>
       <c r="F19" t="n">
-        <v>510</v>
+        <v>1322</v>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.995</v>
       </c>
-      <c r="H19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1108,21 +1167,24 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>75041.5</v>
+        <v>75038.5</v>
       </c>
       <c r="E20" t="n">
         <v>0.9556</v>
       </c>
       <c r="F20" t="n">
-        <v>445</v>
+        <v>1339</v>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
         <v>0.995</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1149,15 +1211,18 @@
         <v>0.9562</v>
       </c>
       <c r="F21" t="n">
-        <v>450</v>
+        <v>1363</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1184,15 +1249,18 @@
         <v>0.9604</v>
       </c>
       <c r="F22" t="n">
-        <v>488</v>
+        <v>1342</v>
       </c>
       <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.995</v>
       </c>
-      <c r="H22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1213,21 +1281,24 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>86159.5</v>
+        <v>86159</v>
       </c>
       <c r="E23" t="n">
         <v>0.9496</v>
       </c>
       <c r="F23" t="n">
-        <v>500</v>
+        <v>1380</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I23" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1254,15 +1325,18 @@
         <v>0.9505</v>
       </c>
       <c r="F24" t="n">
-        <v>550</v>
+        <v>1368</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>0.995</v>
       </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1283,21 +1357,24 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>93495</v>
+        <v>93493</v>
       </c>
       <c r="E25" t="n">
         <v>0.9525</v>
       </c>
       <c r="F25" t="n">
-        <v>528</v>
+        <v>1316</v>
       </c>
       <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.995</v>
       </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1324,15 +1401,18 @@
         <v>0.9500999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>527</v>
+        <v>1388</v>
       </c>
       <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
         <v>0.995</v>
       </c>
-      <c r="H26" t="n">
-        <v>1</v>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1353,21 +1433,24 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>80149</v>
+        <v>80148</v>
       </c>
       <c r="E27" t="n">
         <v>0.953</v>
       </c>
       <c r="F27" t="n">
-        <v>407</v>
+        <v>1318</v>
       </c>
       <c r="G27" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1394,15 +1477,18 @@
         <v>0.9557</v>
       </c>
       <c r="F28" t="n">
-        <v>460</v>
+        <v>1451</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1429,15 +1515,18 @@
         <v>0.9524</v>
       </c>
       <c r="F29" t="n">
-        <v>488</v>
+        <v>1331</v>
       </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>0.995</v>
       </c>
-      <c r="H29" t="n">
-        <v>1</v>
-      </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1458,21 +1547,24 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>89574.5</v>
+        <v>89571</v>
       </c>
       <c r="E30" t="n">
         <v>0.9412</v>
       </c>
       <c r="F30" t="n">
-        <v>513</v>
+        <v>1408</v>
       </c>
       <c r="G30" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
-      </c>
-      <c r="I30" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1499,15 +1591,18 @@
         <v>0.9519</v>
       </c>
       <c r="F31" t="n">
-        <v>463</v>
+        <v>1401</v>
       </c>
       <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
         <v>0.995</v>
       </c>
-      <c r="H31" t="n">
-        <v>1</v>
-      </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1534,15 +1629,18 @@
         <v>0.9547</v>
       </c>
       <c r="F32" t="n">
-        <v>504</v>
+        <v>1375</v>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
         <v>0.995</v>
       </c>
-      <c r="H32" t="n">
-        <v>1</v>
-      </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1563,21 +1661,24 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>63963.5</v>
+        <v>63961.5</v>
       </c>
       <c r="E33" t="n">
         <v>0.9423</v>
       </c>
       <c r="F33" t="n">
-        <v>418</v>
+        <v>1311</v>
       </c>
       <c r="G33" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
-      </c>
-      <c r="I33" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1604,15 +1705,18 @@
         <v>0.9555</v>
       </c>
       <c r="F34" t="n">
-        <v>452</v>
+        <v>1324</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1639,15 +1743,18 @@
         <v>0.9468</v>
       </c>
       <c r="F35" t="n">
-        <v>508</v>
+        <v>1355</v>
       </c>
       <c r="G35" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I35" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1674,15 +1781,18 @@
         <v>0.9537</v>
       </c>
       <c r="F36" t="n">
-        <v>542</v>
+        <v>1645</v>
       </c>
       <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
         <v>0.4975</v>
       </c>
-      <c r="H36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1703,21 +1813,24 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>90185.5</v>
+        <v>90184.5</v>
       </c>
       <c r="E37" t="n">
         <v>0.9559</v>
       </c>
       <c r="F37" t="n">
-        <v>431</v>
+        <v>1413</v>
       </c>
       <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
         <v>0.995</v>
       </c>
-      <c r="H37" t="n">
-        <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1744,15 +1857,18 @@
         <v>0.9563</v>
       </c>
       <c r="F38" t="n">
-        <v>472</v>
+        <v>1386</v>
       </c>
       <c r="G38" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
-      </c>
-      <c r="I38" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1773,21 +1889,24 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>81714.5</v>
+        <v>81712.5</v>
       </c>
       <c r="E39" t="n">
         <v>0.9595</v>
       </c>
       <c r="F39" t="n">
-        <v>472</v>
+        <v>1393</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
-      </c>
-      <c r="I39" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1808,21 +1927,24 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>88479</v>
+        <v>86119</v>
       </c>
       <c r="E40" t="n">
         <v>0.9409</v>
       </c>
       <c r="F40" t="n">
-        <v>544</v>
+        <v>1430</v>
       </c>
       <c r="G40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" t="n">
         <v>0.4975</v>
       </c>
-      <c r="H40" t="n">
-        <v>1</v>
-      </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1843,21 +1965,24 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>84788</v>
+        <v>84787</v>
       </c>
       <c r="E41" t="n">
         <v>0.9525</v>
       </c>
       <c r="F41" t="n">
-        <v>455</v>
+        <v>1350</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
-      </c>
-      <c r="I41" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1884,15 +2009,18 @@
         <v>0.9446</v>
       </c>
       <c r="F42" t="n">
-        <v>335</v>
+        <v>1360</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1913,21 +2041,24 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>65725.5</v>
+        <v>65723.5</v>
       </c>
       <c r="E43" t="n">
         <v>0.9543</v>
       </c>
       <c r="F43" t="n">
-        <v>451</v>
+        <v>1291</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1954,15 +2085,18 @@
         <v>0.9491000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>393</v>
+        <v>1304</v>
       </c>
       <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
         <v>0.995</v>
       </c>
-      <c r="H44" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -1989,15 +2123,18 @@
         <v>0.9637</v>
       </c>
       <c r="F45" t="n">
-        <v>538</v>
+        <v>1412</v>
       </c>
       <c r="G45" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
-      </c>
-      <c r="I45" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2018,21 +2155,24 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>95895.5</v>
+        <v>95890.5</v>
       </c>
       <c r="E46" t="n">
         <v>0.9566</v>
       </c>
       <c r="F46" t="n">
-        <v>641</v>
+        <v>1457</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2059,15 +2199,18 @@
         <v>0.9571</v>
       </c>
       <c r="F47" t="n">
-        <v>558</v>
+        <v>1386</v>
       </c>
       <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
         <v>0.995</v>
       </c>
-      <c r="H47" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2094,15 +2237,18 @@
         <v>0.9419999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>483</v>
+        <v>1248</v>
       </c>
       <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
         <v>0.796</v>
       </c>
-      <c r="H48" t="n">
-        <v>1</v>
-      </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2123,21 +2269,24 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>95927.5</v>
+        <v>95206</v>
       </c>
       <c r="E49" t="n">
         <v>0.9571</v>
       </c>
       <c r="F49" t="n">
-        <v>500</v>
+        <v>1362</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8955</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
-      </c>
-      <c r="I49" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2164,15 +2313,18 @@
         <v>0.9459</v>
       </c>
       <c r="F50" t="n">
-        <v>480</v>
+        <v>1382</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2199,15 +2351,18 @@
         <v>0.9627</v>
       </c>
       <c r="F51" t="n">
-        <v>596</v>
+        <v>1306</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2228,21 +2383,24 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>70809.5</v>
+        <v>70806.5</v>
       </c>
       <c r="E52" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>425</v>
+        <v>1353</v>
       </c>
       <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.995</v>
       </c>
-      <c r="H52" t="n">
-        <v>1</v>
-      </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2269,15 +2427,18 @@
         <v>0.9504</v>
       </c>
       <c r="F53" t="n">
-        <v>358</v>
+        <v>1300</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2304,15 +2465,18 @@
         <v>0.9637</v>
       </c>
       <c r="F54" t="n">
-        <v>511</v>
+        <v>1361</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2333,21 +2497,24 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>91815</v>
+        <v>91813</v>
       </c>
       <c r="E55" t="n">
         <v>0.9474</v>
       </c>
       <c r="F55" t="n">
-        <v>533</v>
+        <v>1344</v>
       </c>
       <c r="G55" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2374,15 +2541,18 @@
         <v>0.9554</v>
       </c>
       <c r="F56" t="n">
-        <v>543</v>
+        <v>1374</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
-      </c>
-      <c r="I56" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2403,21 +2573,24 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>67799.5</v>
+        <v>67797.5</v>
       </c>
       <c r="E57" t="n">
         <v>0.9484</v>
       </c>
       <c r="F57" t="n">
-        <v>404</v>
+        <v>1329</v>
       </c>
       <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.796</v>
       </c>
-      <c r="H57" t="n">
-        <v>1</v>
-      </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2444,15 +2617,18 @@
         <v>0.9516</v>
       </c>
       <c r="F58" t="n">
-        <v>425</v>
+        <v>1296</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
-      </c>
-      <c r="I58" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2473,21 +2649,24 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>88224.5</v>
+        <v>88222</v>
       </c>
       <c r="E59" t="n">
         <v>0.9478</v>
       </c>
       <c r="F59" t="n">
-        <v>475</v>
+        <v>1410</v>
       </c>
       <c r="G59" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
-      </c>
-      <c r="I59" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2508,21 +2687,24 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>89838</v>
+        <v>89003</v>
       </c>
       <c r="E60" t="n">
         <v>0.9510999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>503</v>
+        <v>1336</v>
       </c>
       <c r="G60" t="n">
-        <v>0.8955</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>1</v>
-      </c>
-      <c r="I60" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2543,21 +2725,24 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>71268.5</v>
+        <v>71083</v>
       </c>
       <c r="E61" t="n">
         <v>0.9350000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>717</v>
+        <v>1266</v>
       </c>
       <c r="G61" t="n">
-        <v>0.8955</v>
+        <v>3</v>
       </c>
       <c r="H61" t="n">
-        <v>1</v>
-      </c>
-      <c r="I61" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2578,21 +2763,24 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>88025.5</v>
+        <v>88025</v>
       </c>
       <c r="E62" t="n">
         <v>0.9596</v>
       </c>
       <c r="F62" t="n">
-        <v>525</v>
+        <v>1414</v>
       </c>
       <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
         <v>0.995</v>
       </c>
-      <c r="H62" t="n">
-        <v>1</v>
-      </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2613,21 +2801,24 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>71086</v>
+        <v>71085.5</v>
       </c>
       <c r="E63" t="n">
         <v>0.95</v>
       </c>
       <c r="F63" t="n">
-        <v>638</v>
+        <v>1293</v>
       </c>
       <c r="G63" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2654,15 +2845,18 @@
         <v>0.9548</v>
       </c>
       <c r="F64" t="n">
-        <v>417</v>
+        <v>1341</v>
       </c>
       <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
         <v>0.995</v>
       </c>
-      <c r="H64" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>1</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2689,15 +2883,18 @@
         <v>0.9468</v>
       </c>
       <c r="F65" t="n">
-        <v>529</v>
+        <v>1400</v>
       </c>
       <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
         <v>0.995</v>
       </c>
-      <c r="H65" t="n">
-        <v>1</v>
-      </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2718,21 +2915,24 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>77454.5</v>
+        <v>77431</v>
       </c>
       <c r="E66" t="n">
         <v>0.9510999999999999</v>
       </c>
       <c r="F66" t="n">
-        <v>376</v>
+        <v>1380</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8955</v>
+        <v>2</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
-      </c>
-      <c r="I66" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I66" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2759,15 +2959,18 @@
         <v>0.9552</v>
       </c>
       <c r="F67" t="n">
-        <v>532</v>
+        <v>1331</v>
       </c>
       <c r="G67" t="n">
-        <v>0.8955</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
-      </c>
-      <c r="I67" t="inlineStr">
+        <v>0.8955</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2794,15 +2997,18 @@
         <v>0.9471000000000001</v>
       </c>
       <c r="F68" t="n">
-        <v>344</v>
+        <v>1319</v>
       </c>
       <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
         <v>0.995</v>
       </c>
-      <c r="H68" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
